--- a/气象/表格文件/多站记录或比较/阈值&连续 天数/国家站/国家站单冬 -40 天数(达到20天).xlsx
+++ b/气象/表格文件/多站记录或比较/阈值&连续 天数/国家站/国家站单冬 -40 天数(达到20天).xlsx
@@ -669,12 +669,21 @@
     <xf numFmtId="17" fontId="20" fillId="9" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="22" fillId="2" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="3"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -683,15 +692,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="22" fillId="2" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="3"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1032,24 +1032,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="60" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="29"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="28"/>
     </row>
     <row r="2" spans="1:7" ht="30.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="27" t="s">
+      <c r="B2" s="29"/>
+      <c r="C2" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="28"/>
-      <c r="E2" s="30" t="s">
+      <c r="D2" s="31"/>
+      <c r="E2" s="24" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       <c r="D3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="31">
+      <c r="E3" s="25">
         <v>-49.6</v>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       <c r="D4" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="25">
         <v>-50</v>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       <c r="D5" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="25">
         <v>-52.3</v>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       <c r="D6" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="25">
         <v>-50.8</v>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       <c r="D7" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="25">
         <v>-48</v>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       <c r="D8" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="25">
         <v>-49.8</v>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       <c r="D9" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="25">
         <v>-46.8</v>
       </c>
       <c r="F9" s="2"/>
@@ -1187,7 +1187,7 @@
       <c r="D10" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="25">
         <v>-45.2</v>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       <c r="D11" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="25">
         <v>-46.7</v>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       <c r="D12" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="25">
         <v>-48.2</v>
       </c>
       <c r="F12" s="3"/>
@@ -1240,7 +1240,7 @@
       <c r="D13" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="25">
         <v>-46.5</v>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       <c r="D14" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="25">
         <v>-51.5</v>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       <c r="D15" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="25">
         <v>-49.7</v>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       <c r="D16" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="25">
         <v>-47.7</v>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       <c r="D17" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="25">
         <v>-49.6</v>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       <c r="D18" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="25">
         <v>-46</v>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       <c r="D19" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="31">
+      <c r="E19" s="25">
         <v>-47.9</v>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       <c r="D20" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="31">
+      <c r="E20" s="25">
         <v>-48.5</v>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
       <c r="D21" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="25">
         <v>-48.1</v>
       </c>
     </row>
@@ -1388,5 +1388,6 @@
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>